--- a/docs/data/beidan_26088_dashboard.xlsx
+++ b/docs/data/beidan_26088_dashboard.xlsx
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26088期 比赛看板（皇冠历史相同亚盘） — 2026-08-25</t>
+          <t>⚽ 北京单场26088期 比赛看板（皇冠历史相同亚盘） — 2026-08-26</t>
         </is>
       </c>
     </row>
@@ -644,10 +644,14 @@
       </c>
       <c r="G4" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -700,10 +704,14 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -756,10 +764,14 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -812,10 +824,14 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -868,10 +884,14 @@
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -924,10 +944,14 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -980,10 +1004,14 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr"/>
+          <t>1:3</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -1036,10 +1064,14 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -1092,10 +1124,14 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -1148,10 +1184,14 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr"/>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -1204,10 +1244,14 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -1260,10 +1304,14 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
+          <t>4:0</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -1316,10 +1364,14 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -1372,10 +1424,14 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="inlineStr"/>
+          <t>2:4</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
           <t>受半球/一球</t>
@@ -1428,10 +1484,14 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" s="4" t="inlineStr"/>
+          <t>1:4</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -1484,10 +1544,14 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" s="5" t="inlineStr"/>
+          <t>0:3</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1540,10 +1604,14 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -1596,10 +1664,14 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -1652,10 +1724,14 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr"/>
+          <t>1:5</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -1708,10 +1784,14 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -1764,10 +1844,14 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H24" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -1820,10 +1904,14 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -1876,10 +1964,14 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
+          <t>1:6</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -1932,10 +2024,14 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -1988,10 +2084,14 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -2044,10 +2144,14 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -2100,10 +2204,14 @@
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -2328,20 +2436,24 @@
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr"/>
-      <c r="I34" s="4" t="inlineStr"/>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>受平手/半球</t>
+        </is>
+      </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>41%</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>29%</t>
         </is>
       </c>
     </row>
@@ -3388,20 +3500,24 @@
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="5" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>一球</t>
+        </is>
+      </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>25%</t>
-        </is>
-      </c>
-      <c r="L53" s="6" t="inlineStr">
-        <is>
-          <t>41%</t>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>34%</t>
         </is>
       </c>
     </row>
@@ -3440,20 +3556,24 @@
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr"/>
-      <c r="I54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>半球/一球</t>
+        </is>
+      </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
           <t>38%</t>
         </is>
       </c>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>16%</t>
         </is>
       </c>
     </row>
@@ -3492,20 +3612,24 @@
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="5" t="inlineStr"/>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>38%</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>33%</t>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>一球</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K55" s="8" t="inlineStr">
+        <is>
+          <t>66%</t>
         </is>
       </c>
       <c r="L55" s="5" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>16%</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5284,11 @@
         </is>
       </c>
       <c r="H85" s="5" t="inlineStr"/>
-      <c r="I85" s="5" t="inlineStr"/>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>半球/一球</t>
+        </is>
+      </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
           <t>33%</t>
@@ -5264,20 +5392,24 @@
         </is>
       </c>
       <c r="H87" s="5" t="inlineStr"/>
-      <c r="I87" s="5" t="inlineStr"/>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>受平手/半球</t>
+        </is>
+      </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="K87" s="5" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="L87" s="6" t="inlineStr">
-        <is>
-          <t>39%</t>
+          <t>16%</t>
+        </is>
+      </c>
+      <c r="K87" s="8" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="L87" s="5" t="inlineStr">
+        <is>
+          <t>33%</t>
         </is>
       </c>
     </row>

--- a/docs/data/beidan_26088_dashboard.xlsx
+++ b/docs/data/beidan_26088_dashboard.xlsx
@@ -540,7 +540,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>⚽ 北京单场26088期 比赛看板（皇冠历史相同亚盘） — 2026-08-26</t>
+          <t>⚽ 北京单场26088期 比赛看板（皇冠历史相同亚盘） — 2026-08-27</t>
         </is>
       </c>
     </row>
@@ -2264,10 +2264,14 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="5" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -2320,10 +2324,14 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="inlineStr"/>
+          <t>2:1</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -2376,10 +2384,14 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H33" s="5" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -2432,10 +2444,14 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -2488,10 +2504,14 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H35" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
           <t>半球</t>
@@ -2544,10 +2564,14 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
           <t>一球</t>
@@ -2600,10 +2624,14 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -2656,10 +2684,14 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="inlineStr"/>
+          <t>2:2</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -2712,10 +2744,14 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="5" t="inlineStr"/>
+          <t>0:1</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
           <t>平手</t>
@@ -2768,10 +2804,14 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="inlineStr"/>
+          <t>4:2</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
           <t>球半</t>
@@ -2824,10 +2864,14 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -2880,10 +2924,14 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -2936,10 +2984,14 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr"/>
+          <t>0:0</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>受平手/半球</t>
@@ -2992,10 +3044,14 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr"/>
+          <t>3:2</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -3048,10 +3104,14 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr"/>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
           <t>球半/两球</t>
@@ -3104,10 +3164,14 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr"/>
+          <t>3:1</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
           <t>平手</t>
@@ -3160,10 +3224,14 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -3216,10 +3284,14 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
           <t>半球</t>
@@ -3272,10 +3344,14 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr"/>
+          <t>4:1</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
           <t>一球/球半</t>
@@ -3328,10 +3404,14 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr"/>
+          <t>0:4</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
           <t>受一球</t>
@@ -3384,10 +3464,14 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" s="5" t="inlineStr"/>
+          <t>1:2</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
           <t>平手/半球</t>
@@ -3440,10 +3524,14 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr"/>
+          <t>0:2</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
           <t>受半球</t>
@@ -3496,10 +3584,14 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr"/>
+          <t>1:1</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>负</t>
+        </is>
+      </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -3552,10 +3644,14 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr"/>
+          <t>1:0</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>平</t>
+        </is>
+      </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
           <t>半球/一球</t>
@@ -3608,10 +3704,14 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr"/>
+          <t>3:0</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>胜</t>
+        </is>
+      </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
           <t>一球</t>
@@ -4284,20 +4384,24 @@
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr"/>
-      <c r="I67" s="5" t="inlineStr"/>
-      <c r="J67" s="5" t="inlineStr">
-        <is>
-          <t>34%</t>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>平手/半球</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>36%</t>
         </is>
       </c>
       <c r="K67" s="5" t="inlineStr">
         <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="L67" s="5" t="inlineStr">
-        <is>
-          <t>34%</t>
+          <t>27%</t>
+        </is>
+      </c>
+      <c r="L67" s="6" t="inlineStr">
+        <is>
+          <t>36%</t>
         </is>
       </c>
     </row>
@@ -5232,20 +5336,24 @@
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr"/>
-      <c r="I84" s="4" t="inlineStr"/>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>两球</t>
+        </is>
+      </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="K84" s="4" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>57%</t>
         </is>
       </c>
     </row>
@@ -5340,20 +5448,24 @@
         </is>
       </c>
       <c r="H86" s="4" t="inlineStr"/>
-      <c r="I86" s="4" t="inlineStr"/>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>半球</t>
+        </is>
+      </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>20%</t>
         </is>
       </c>
     </row>
